--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmunip.CAMPUS\source\repos\ABM-Random-Forest\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmunip.CAMPUS\source\repos\ABM-NM-optimization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504325C3-5D65-446C-B0DF-D439C97FDFA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429AD3BC-C01B-4C1B-B0AB-21BA4B32E3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6075" yWindow="2325" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="78">
   <si>
     <t>Mean</t>
   </si>
@@ -236,18 +236,6 @@
   </si>
   <si>
     <t>biomaterial:elastic_modulus:crosslinker_density</t>
-  </si>
-  <si>
-    <t>biomaterial:elastic_modulus:alginate_molecular_weight</t>
-  </si>
-  <si>
-    <t>biomaterial:elastic_modulus:alginate_crosslinker_interaction</t>
-  </si>
-  <si>
-    <t>biomaterial:elastic_modulus:alginate_mw_interaction</t>
-  </si>
-  <si>
-    <t>biomaterial:elastic_modulus:mw_crosslinker_interaction</t>
   </si>
   <si>
     <t>biomaterial:pore_size:crosslinker_effect</t>
@@ -647,7 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="21" customWidth="1"/>
@@ -1934,19 +1922,19 @@
         <v>64</v>
       </c>
       <c r="C51">
-        <v>125</v>
+        <v>-1.619</v>
       </c>
       <c r="D51">
-        <f t="shared" ref="D51:D68" si="2">(F51-E51)/4</f>
+        <f t="shared" ref="D51:D64" si="2">(F51-E51)/4</f>
         <v>0</v>
       </c>
       <c r="E51">
         <f>C51</f>
-        <v>125</v>
+        <v>-1.619</v>
       </c>
       <c r="F51">
         <f>C51</f>
-        <v>125</v>
+        <v>-1.619</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -1966,19 +1954,19 @@
         <v>65</v>
       </c>
       <c r="C52">
-        <v>58</v>
+        <v>8592</v>
       </c>
       <c r="D52">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E52">
-        <f t="shared" ref="E52:E68" si="3">C52</f>
-        <v>58</v>
+        <f t="shared" ref="E52:E64" si="3">C52</f>
+        <v>8592</v>
       </c>
       <c r="F52">
-        <f t="shared" ref="F52:F68" si="4">C52</f>
-        <v>58</v>
+        <f t="shared" ref="F52:F64" si="4">C52</f>
+        <v>8592</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -1995,7 +1983,7 @@
         <v>66</v>
       </c>
       <c r="C53">
-        <v>971</v>
+        <v>1.5E-3</v>
       </c>
       <c r="D53">
         <f t="shared" si="2"/>
@@ -2003,11 +1991,11 @@
       </c>
       <c r="E53">
         <f t="shared" si="3"/>
-        <v>971</v>
+        <v>1.5E-3</v>
       </c>
       <c r="F53">
         <f t="shared" si="4"/>
-        <v>971</v>
+        <v>1.5E-3</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -2024,7 +2012,7 @@
         <v>67</v>
       </c>
       <c r="C54">
-        <v>1.0369999999999999</v>
+        <v>1769.8</v>
       </c>
       <c r="D54">
         <f t="shared" si="2"/>
@@ -2032,11 +2020,11 @@
       </c>
       <c r="E54">
         <f t="shared" si="3"/>
-        <v>1.0369999999999999</v>
+        <v>1769.8</v>
       </c>
       <c r="F54">
         <f t="shared" si="4"/>
-        <v>1.0369999999999999</v>
+        <v>1769.8</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -2053,7 +2041,7 @@
         <v>68</v>
       </c>
       <c r="C55">
-        <v>756</v>
+        <v>258.5</v>
       </c>
       <c r="D55">
         <f t="shared" si="2"/>
@@ -2061,11 +2049,11 @@
       </c>
       <c r="E55">
         <f t="shared" si="3"/>
-        <v>756</v>
+        <v>258.5</v>
       </c>
       <c r="F55">
         <f t="shared" si="4"/>
-        <v>756</v>
+        <v>258.5</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -2082,7 +2070,7 @@
         <v>69</v>
       </c>
       <c r="C56">
-        <v>0.51600000000000001</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="D56">
         <f t="shared" si="2"/>
@@ -2090,11 +2078,11 @@
       </c>
       <c r="E56">
         <f t="shared" si="3"/>
-        <v>0.51600000000000001</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="F56">
         <f t="shared" si="4"/>
-        <v>0.51600000000000001</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -2111,7 +2099,7 @@
         <v>70</v>
       </c>
       <c r="C57">
-        <v>0.16500000000000001</v>
+        <v>7.7850000000000001</v>
       </c>
       <c r="D57">
         <f t="shared" si="2"/>
@@ -2119,11 +2107,11 @@
       </c>
       <c r="E57">
         <f t="shared" si="3"/>
-        <v>0.16500000000000001</v>
+        <v>7.7850000000000001</v>
       </c>
       <c r="F57">
         <f t="shared" si="4"/>
-        <v>0.16500000000000001</v>
+        <v>7.7850000000000001</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -2140,7 +2128,7 @@
         <v>71</v>
       </c>
       <c r="C58">
-        <v>1769.8</v>
+        <v>0.15</v>
       </c>
       <c r="D58">
         <f t="shared" si="2"/>
@@ -2148,11 +2136,11 @@
       </c>
       <c r="E58">
         <f t="shared" si="3"/>
-        <v>1769.8</v>
+        <v>0.15</v>
       </c>
       <c r="F58">
         <f t="shared" si="4"/>
-        <v>1769.8</v>
+        <v>0.15</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -2169,7 +2157,7 @@
         <v>72</v>
       </c>
       <c r="C59">
-        <v>258.5</v>
+        <v>1.36</v>
       </c>
       <c r="D59">
         <f t="shared" si="2"/>
@@ -2177,11 +2165,11 @@
       </c>
       <c r="E59">
         <f t="shared" si="3"/>
-        <v>258.5</v>
+        <v>1.36</v>
       </c>
       <c r="F59">
         <f t="shared" si="4"/>
-        <v>258.5</v>
+        <v>1.36</v>
       </c>
       <c r="G59">
         <v>1</v>
@@ -2198,7 +2186,7 @@
         <v>73</v>
       </c>
       <c r="C60">
-        <v>0.23400000000000001</v>
+        <v>72.477999999999994</v>
       </c>
       <c r="D60">
         <f t="shared" si="2"/>
@@ -2206,11 +2194,11 @@
       </c>
       <c r="E60">
         <f t="shared" si="3"/>
-        <v>0.23400000000000001</v>
+        <v>72.477999999999994</v>
       </c>
       <c r="F60">
         <f t="shared" si="4"/>
-        <v>0.23400000000000001</v>
+        <v>72.477999999999994</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -2227,7 +2215,7 @@
         <v>74</v>
       </c>
       <c r="C61">
-        <v>7.7850000000000001</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="D61">
         <f t="shared" si="2"/>
@@ -2235,11 +2223,11 @@
       </c>
       <c r="E61">
         <f t="shared" si="3"/>
-        <v>7.7850000000000001</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="F61">
         <f t="shared" si="4"/>
-        <v>7.7850000000000001</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -2256,7 +2244,7 @@
         <v>75</v>
       </c>
       <c r="C62">
-        <v>0.15</v>
+        <v>22.033999999999999</v>
       </c>
       <c r="D62">
         <f t="shared" si="2"/>
@@ -2264,11 +2252,11 @@
       </c>
       <c r="E62">
         <f t="shared" si="3"/>
-        <v>0.15</v>
+        <v>22.033999999999999</v>
       </c>
       <c r="F62">
         <f t="shared" si="4"/>
-        <v>0.15</v>
+        <v>22.033999999999999</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -2285,7 +2273,7 @@
         <v>76</v>
       </c>
       <c r="C63">
-        <v>1.36</v>
+        <v>3.2839999999999998</v>
       </c>
       <c r="D63">
         <f t="shared" si="2"/>
@@ -2293,11 +2281,11 @@
       </c>
       <c r="E63">
         <f t="shared" si="3"/>
-        <v>1.36</v>
+        <v>3.2839999999999998</v>
       </c>
       <c r="F63">
         <f t="shared" si="4"/>
-        <v>1.36</v>
+        <v>3.2839999999999998</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -2314,7 +2302,7 @@
         <v>77</v>
       </c>
       <c r="C64">
-        <v>72.477999999999994</v>
+        <v>35.752000000000002</v>
       </c>
       <c r="D64">
         <f t="shared" si="2"/>
@@ -2322,132 +2310,16 @@
       </c>
       <c r="E64">
         <f t="shared" si="3"/>
-        <v>72.477999999999994</v>
+        <v>35.752000000000002</v>
       </c>
       <c r="F64">
         <f t="shared" si="4"/>
-        <v>72.477999999999994</v>
+        <v>35.752000000000002</v>
       </c>
       <c r="G64">
         <v>1</v>
       </c>
       <c r="H64" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="s">
-        <v>78</v>
-      </c>
-      <c r="C65">
-        <v>0.13100000000000001</v>
-      </c>
-      <c r="D65">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E65">
-        <f t="shared" si="3"/>
-        <v>0.13100000000000001</v>
-      </c>
-      <c r="F65">
-        <f t="shared" si="4"/>
-        <v>0.13100000000000001</v>
-      </c>
-      <c r="G65">
-        <v>1</v>
-      </c>
-      <c r="H65" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="s">
-        <v>79</v>
-      </c>
-      <c r="C66">
-        <v>22.033999999999999</v>
-      </c>
-      <c r="D66">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E66">
-        <f t="shared" si="3"/>
-        <v>22.033999999999999</v>
-      </c>
-      <c r="F66">
-        <f t="shared" si="4"/>
-        <v>22.033999999999999</v>
-      </c>
-      <c r="G66">
-        <v>1</v>
-      </c>
-      <c r="H66" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" t="s">
-        <v>80</v>
-      </c>
-      <c r="C67">
-        <v>3.2839999999999998</v>
-      </c>
-      <c r="D67">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E67">
-        <f t="shared" si="3"/>
-        <v>3.2839999999999998</v>
-      </c>
-      <c r="F67">
-        <f t="shared" si="4"/>
-        <v>3.2839999999999998</v>
-      </c>
-      <c r="G67">
-        <v>1</v>
-      </c>
-      <c r="H67" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" t="s">
-        <v>81</v>
-      </c>
-      <c r="C68">
-        <v>35.752000000000002</v>
-      </c>
-      <c r="D68">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E68">
-        <f t="shared" si="3"/>
-        <v>35.752000000000002</v>
-      </c>
-      <c r="F68">
-        <f t="shared" si="4"/>
-        <v>35.752000000000002</v>
-      </c>
-      <c r="G68">
-        <v>1</v>
-      </c>
-      <c r="H68" t="s">
         <v>10</v>
       </c>
     </row>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmunip.CAMPUS\source\repos\ABM-NM-optimization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429AD3BC-C01B-4C1B-B0AB-21BA4B32E3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC63000-F8F3-4288-85C6-D92628EDD8D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6075" yWindow="2325" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -232,9 +232,6 @@
     <t>biomaterial:elastic_modulus:intercept</t>
   </si>
   <si>
-    <t>biomaterial:elastic_modulus:alginate_concentration</t>
-  </si>
-  <si>
     <t>biomaterial:elastic_modulus:crosslinker_density</t>
   </si>
   <si>
@@ -269,6 +266,9 @@
   </si>
   <si>
     <t>biomaterial:swell_ratio:alginate_crosslinker_interaction</t>
+  </si>
+  <si>
+    <t>biomaterial:elastic_modulus:alginate_molecular_weight</t>
   </si>
 </sst>
 </file>
@@ -1980,7 +1980,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C53">
         <v>1.5E-3</v>
@@ -2009,7 +2009,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C54">
         <v>1769.8</v>
@@ -2038,7 +2038,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C55">
         <v>258.5</v>
@@ -2067,7 +2067,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C56">
         <v>0.23400000000000001</v>
@@ -2096,7 +2096,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C57">
         <v>7.7850000000000001</v>
@@ -2125,7 +2125,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C58">
         <v>0.15</v>
@@ -2154,7 +2154,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C59">
         <v>1.36</v>
@@ -2183,7 +2183,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C60">
         <v>72.477999999999994</v>
@@ -2212,7 +2212,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C61">
         <v>0.13100000000000001</v>
@@ -2241,7 +2241,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C62">
         <v>22.033999999999999</v>
@@ -2270,7 +2270,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C63">
         <v>3.2839999999999998</v>
@@ -2299,7 +2299,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C64">
         <v>35.752000000000002</v>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmunip.CAMPUS\source\repos\ABM-NM-optimization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC63000-F8F3-4288-85C6-D92628EDD8D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C141CB2-284A-4BA7-9291-C48AA37AE700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6075" yWindow="2325" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="81">
   <si>
     <t>Mean</t>
   </si>
@@ -269,6 +269,15 @@
   </si>
   <si>
     <t>biomaterial:elastic_modulus:alginate_molecular_weight</t>
+  </si>
+  <si>
+    <t>stem:proliferation:static_probability</t>
+  </si>
+  <si>
+    <t>stem:differentiation:static_probability</t>
+  </si>
+  <si>
+    <t>progen:differentiation:static_probability</t>
   </si>
 </sst>
 </file>
@@ -316,11 +325,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -635,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="21" customWidth="1"/>
@@ -710,7 +720,7 @@
         <v>10</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D50" si="0">(F3-E3)/4</f>
+        <f t="shared" ref="D3:D53" si="0">(F3-E3)/4</f>
         <v>24.75</v>
       </c>
       <c r="E3">
@@ -1298,23 +1308,23 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="C26">
-        <v>0.8</v>
+        <v>40</v>
       </c>
       <c r="D26">
         <f t="shared" si="0"/>
-        <v>0.24975</v>
-      </c>
-      <c r="E26">
-        <v>1E-3</v>
+        <v>15</v>
+      </c>
+      <c r="E26" s="4">
+        <v>10</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1322,10 +1332,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C27">
-        <v>1E-3</v>
+        <v>0.8</v>
       </c>
       <c r="D27">
         <f t="shared" si="0"/>
@@ -1346,20 +1356,20 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C28">
-        <v>0.5</v>
+        <v>1E-3</v>
       </c>
       <c r="D28">
         <f t="shared" si="0"/>
-        <v>2.4997500000000001</v>
+        <v>0.24975</v>
       </c>
       <c r="E28">
         <v>1E-3</v>
       </c>
       <c r="F28">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1370,26 +1380,23 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C29">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="D29">
         <f t="shared" si="0"/>
-        <v>5.0000000000000017E-2</v>
-      </c>
-      <c r="E29" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="F29" s="2">
-        <v>0.8</v>
+        <v>2.4997500000000001</v>
+      </c>
+      <c r="E29">
+        <v>1E-3</v>
+      </c>
+      <c r="F29">
+        <v>10</v>
       </c>
       <c r="G29">
-        <v>4</v>
-      </c>
-      <c r="H29" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1397,20 +1404,20 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C30">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="D30">
         <f t="shared" si="0"/>
-        <v>4.9999999999999989E-2</v>
+        <v>5.0000000000000017E-2</v>
       </c>
       <c r="E30" s="2">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="F30" s="2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G30">
         <v>4</v>
@@ -1424,23 +1431,23 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="C31">
-        <v>1E-3</v>
+        <v>20</v>
       </c>
       <c r="D31">
         <f t="shared" si="0"/>
-        <v>0.24975</v>
-      </c>
-      <c r="E31">
-        <v>1E-3</v>
-      </c>
-      <c r="F31">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="E31" s="4">
+        <v>10</v>
+      </c>
+      <c r="F31" s="4">
+        <v>70</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1448,23 +1455,26 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C32">
-        <v>48</v>
+        <v>0.5</v>
       </c>
       <c r="D32">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>4.9999999999999989E-2</v>
       </c>
       <c r="E32" s="2">
-        <v>47</v>
+        <v>0.4</v>
       </c>
       <c r="F32" s="2">
-        <v>49</v>
+        <v>0.6</v>
       </c>
       <c r="G32">
         <v>4</v>
+      </c>
+      <c r="H32" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1472,20 +1482,20 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C33">
-        <v>30.46</v>
+        <v>1E-3</v>
       </c>
       <c r="D33">
         <f t="shared" si="0"/>
-        <v>22.5</v>
-      </c>
-      <c r="E33" s="2">
-        <v>10</v>
-      </c>
-      <c r="F33" s="2">
-        <v>100</v>
+        <v>0.24975</v>
+      </c>
+      <c r="E33">
+        <v>1E-3</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -1496,23 +1506,26 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34">
+        <v>48</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="E34" s="2">
         <v>47</v>
       </c>
-      <c r="C34">
-        <v>0.1</v>
-      </c>
-      <c r="D34">
-        <f t="shared" si="0"/>
-        <v>0.24975</v>
-      </c>
-      <c r="E34">
-        <v>1E-3</v>
-      </c>
-      <c r="F34">
-        <v>1</v>
+      <c r="F34" s="2">
+        <v>49</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="H34" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1520,20 +1533,20 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C35">
-        <v>0.11</v>
+        <v>30.46</v>
       </c>
       <c r="D35">
         <f t="shared" si="0"/>
-        <v>0.27225000000000005</v>
+        <v>22.5</v>
       </c>
       <c r="E35" s="2">
-        <v>1.0999999999999999E-2</v>
+        <v>10</v>
       </c>
       <c r="F35" s="2">
-        <v>1.1000000000000001</v>
+        <v>100</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -1547,26 +1560,23 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C36">
-        <v>0.83</v>
+        <v>0.1</v>
       </c>
       <c r="D36">
         <f t="shared" si="0"/>
-        <v>2.0542500000000001</v>
-      </c>
-      <c r="E36" s="2">
-        <v>8.3000000000000004E-2</v>
-      </c>
-      <c r="F36" s="2">
-        <v>8.3000000000000007</v>
+        <v>0.24975</v>
+      </c>
+      <c r="E36">
+        <v>1E-3</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
       </c>
       <c r="G36">
-        <v>1</v>
-      </c>
-      <c r="H36" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -1574,23 +1584,26 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>0.11</v>
       </c>
       <c r="D37">
         <f t="shared" si="0"/>
-        <v>2.25</v>
-      </c>
-      <c r="E37">
-        <v>1</v>
-      </c>
-      <c r="F37">
-        <v>10</v>
+        <v>0.27225000000000005</v>
+      </c>
+      <c r="E37" s="2">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="F37" s="2">
+        <v>1.1000000000000001</v>
       </c>
       <c r="G37">
         <v>1</v>
+      </c>
+      <c r="H37" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -1598,23 +1611,26 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C38">
-        <v>2.58</v>
+        <v>0.83</v>
       </c>
       <c r="D38">
         <f t="shared" si="0"/>
-        <v>2.25</v>
-      </c>
-      <c r="E38">
-        <v>1</v>
-      </c>
-      <c r="F38">
-        <v>10</v>
+        <v>2.0542500000000001</v>
+      </c>
+      <c r="E38" s="2">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="F38" s="2">
+        <v>8.3000000000000007</v>
       </c>
       <c r="G38">
         <v>1</v>
+      </c>
+      <c r="H38" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -1622,26 +1638,23 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E39" s="2">
-        <v>0</v>
-      </c>
-      <c r="F39" s="2">
-        <v>0</v>
+        <v>2.25</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="F39">
+        <v>10</v>
       </c>
       <c r="G39">
         <v>1</v>
-      </c>
-      <c r="H39" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -1649,10 +1662,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>2.58</v>
       </c>
       <c r="D40">
         <f t="shared" si="0"/>
@@ -1673,23 +1686,26 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C41">
-        <v>15.31</v>
+        <v>0</v>
       </c>
       <c r="D41">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="E41">
-        <v>10</v>
-      </c>
-      <c r="F41">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0</v>
+      </c>
+      <c r="F41" s="2">
+        <v>0</v>
       </c>
       <c r="G41">
         <v>1</v>
+      </c>
+      <c r="H41" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -1697,10 +1713,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D42">
         <f t="shared" si="0"/>
@@ -1713,7 +1729,7 @@
         <v>10</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -1721,26 +1737,23 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="C43">
-        <v>0.11</v>
+        <v>20</v>
       </c>
       <c r="D43">
-        <f t="shared" ref="D43" si="1">(F43-E43)/4</f>
-        <v>0.27225000000000005</v>
-      </c>
-      <c r="E43" s="2">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="F43" s="2">
-        <v>1.1000000000000001</v>
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="E43">
+        <v>10</v>
+      </c>
+      <c r="F43">
+        <v>70</v>
       </c>
       <c r="G43">
-        <v>1</v>
-      </c>
-      <c r="H43" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -1748,20 +1761,20 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C44">
-        <v>1.3</v>
+        <v>15.31</v>
       </c>
       <c r="D44">
-        <f>(F44-E44)/4</f>
-        <v>3.2174999999999998</v>
-      </c>
-      <c r="E44" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="F44" s="2">
-        <v>13</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="E44">
+        <v>10</v>
+      </c>
+      <c r="F44">
+        <v>50</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -1775,23 +1788,23 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>58</v>
-      </c>
-      <c r="C45" s="1">
-        <v>10</v>
+        <v>55</v>
+      </c>
+      <c r="C45">
+        <v>5</v>
       </c>
       <c r="D45">
         <f t="shared" si="0"/>
-        <v>24.75</v>
+        <v>2.25</v>
       </c>
       <c r="E45">
         <v>1</v>
       </c>
       <c r="F45">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -1799,23 +1812,26 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>59</v>
-      </c>
-      <c r="C46" s="1">
-        <v>6.45</v>
+        <v>56</v>
+      </c>
+      <c r="C46">
+        <v>0.11</v>
       </c>
       <c r="D46">
-        <f t="shared" si="0"/>
-        <v>15.963749999999999</v>
-      </c>
-      <c r="E46">
-        <v>0.64500000000000002</v>
-      </c>
-      <c r="F46">
-        <v>64.5</v>
+        <f t="shared" ref="D46" si="1">(F46-E46)/4</f>
+        <v>0.27225000000000005</v>
+      </c>
+      <c r="E46" s="2">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1000000000000001</v>
       </c>
       <c r="G46">
         <v>1</v>
+      </c>
+      <c r="H46" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -1823,23 +1839,26 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>60</v>
-      </c>
-      <c r="C47" s="1">
-        <v>3.6</v>
+        <v>57</v>
+      </c>
+      <c r="C47">
+        <v>1.3</v>
       </c>
       <c r="D47">
-        <f t="shared" si="0"/>
-        <v>8.91</v>
-      </c>
-      <c r="E47">
-        <v>0.36</v>
-      </c>
-      <c r="F47">
-        <v>36</v>
+        <f>(F47-E47)/4</f>
+        <v>3.2174999999999998</v>
+      </c>
+      <c r="E47" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="F47" s="2">
+        <v>13</v>
       </c>
       <c r="G47">
         <v>1</v>
+      </c>
+      <c r="H47" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -1847,20 +1866,20 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C48" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D48">
         <f t="shared" si="0"/>
-        <v>49.5</v>
+        <v>24.75</v>
       </c>
       <c r="E48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F48">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -1871,20 +1890,20 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C49" s="1">
-        <v>38</v>
+        <v>6.45</v>
       </c>
       <c r="D49">
         <f t="shared" si="0"/>
-        <v>94.05</v>
+        <v>15.963749999999999</v>
       </c>
       <c r="E49">
-        <v>3.8</v>
+        <v>0.64500000000000002</v>
       </c>
       <c r="F49">
-        <v>380</v>
+        <v>64.5</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -1895,20 +1914,20 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C50" s="1">
-        <v>16.600000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="D50">
         <f t="shared" si="0"/>
-        <v>41.085000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="E50">
-        <v>1.66</v>
+        <v>0.36</v>
       </c>
       <c r="F50">
-        <v>166</v>
+        <v>36</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -1919,31 +1938,23 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>64</v>
-      </c>
-      <c r="C51">
-        <v>-1.619</v>
+        <v>61</v>
+      </c>
+      <c r="C51" s="1">
+        <v>20</v>
       </c>
       <c r="D51">
-        <f t="shared" ref="D51:D64" si="2">(F51-E51)/4</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>49.5</v>
       </c>
       <c r="E51">
-        <f>C51</f>
-        <v>-1.619</v>
+        <v>2</v>
       </c>
       <c r="F51">
-        <f>C51</f>
-        <v>-1.619</v>
+        <v>200</v>
       </c>
       <c r="G51">
         <v>1</v>
-      </c>
-      <c r="H51" t="s">
-        <v>10</v>
-      </c>
-      <c r="J51" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -1951,28 +1962,23 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>65</v>
-      </c>
-      <c r="C52">
-        <v>8592</v>
+        <v>62</v>
+      </c>
+      <c r="C52" s="1">
+        <v>38</v>
       </c>
       <c r="D52">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>94.05</v>
       </c>
       <c r="E52">
-        <f t="shared" ref="E52:E64" si="3">C52</f>
-        <v>8592</v>
+        <v>3.8</v>
       </c>
       <c r="F52">
-        <f t="shared" ref="F52:F64" si="4">C52</f>
-        <v>8592</v>
+        <v>380</v>
       </c>
       <c r="G52">
         <v>1</v>
-      </c>
-      <c r="H52" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -1980,28 +1986,23 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>77</v>
-      </c>
-      <c r="C53">
-        <v>1.5E-3</v>
+        <v>63</v>
+      </c>
+      <c r="C53" s="1">
+        <v>16.600000000000001</v>
       </c>
       <c r="D53">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>41.085000000000001</v>
       </c>
       <c r="E53">
-        <f t="shared" si="3"/>
-        <v>1.5E-3</v>
+        <v>1.66</v>
       </c>
       <c r="F53">
-        <f t="shared" si="4"/>
-        <v>1.5E-3</v>
+        <v>166</v>
       </c>
       <c r="G53">
         <v>1</v>
-      </c>
-      <c r="H53" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -2009,28 +2010,31 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C54">
-        <v>1769.8</v>
+        <v>-1.619</v>
       </c>
       <c r="D54">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="D54:D67" si="2">(F54-E54)/4</f>
         <v>0</v>
       </c>
       <c r="E54">
-        <f t="shared" si="3"/>
-        <v>1769.8</v>
+        <f>C54</f>
+        <v>-1.619</v>
       </c>
       <c r="F54">
-        <f t="shared" si="4"/>
-        <v>1769.8</v>
+        <f>C54</f>
+        <v>-1.619</v>
       </c>
       <c r="G54">
         <v>1</v>
       </c>
       <c r="H54" t="s">
         <v>10</v>
+      </c>
+      <c r="J54" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -2038,22 +2042,22 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C55">
-        <v>258.5</v>
+        <v>8592</v>
       </c>
       <c r="D55">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E55">
-        <f t="shared" si="3"/>
-        <v>258.5</v>
+        <f t="shared" ref="E55:E67" si="3">C55</f>
+        <v>8592</v>
       </c>
       <c r="F55">
-        <f t="shared" si="4"/>
-        <v>258.5</v>
+        <f t="shared" ref="F55:F67" si="4">C55</f>
+        <v>8592</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -2067,10 +2071,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C56">
-        <v>0.23400000000000001</v>
+        <v>1.5E-3</v>
       </c>
       <c r="D56">
         <f t="shared" si="2"/>
@@ -2078,11 +2082,11 @@
       </c>
       <c r="E56">
         <f t="shared" si="3"/>
-        <v>0.23400000000000001</v>
+        <v>1.5E-3</v>
       </c>
       <c r="F56">
         <f t="shared" si="4"/>
-        <v>0.23400000000000001</v>
+        <v>1.5E-3</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -2096,10 +2100,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C57">
-        <v>7.7850000000000001</v>
+        <v>1769.8</v>
       </c>
       <c r="D57">
         <f t="shared" si="2"/>
@@ -2107,11 +2111,11 @@
       </c>
       <c r="E57">
         <f t="shared" si="3"/>
-        <v>7.7850000000000001</v>
+        <v>1769.8</v>
       </c>
       <c r="F57">
         <f t="shared" si="4"/>
-        <v>7.7850000000000001</v>
+        <v>1769.8</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -2125,10 +2129,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C58">
-        <v>0.15</v>
+        <v>258.5</v>
       </c>
       <c r="D58">
         <f t="shared" si="2"/>
@@ -2136,11 +2140,11 @@
       </c>
       <c r="E58">
         <f t="shared" si="3"/>
-        <v>0.15</v>
+        <v>258.5</v>
       </c>
       <c r="F58">
         <f t="shared" si="4"/>
-        <v>0.15</v>
+        <v>258.5</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -2154,10 +2158,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C59">
-        <v>1.36</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="D59">
         <f t="shared" si="2"/>
@@ -2165,11 +2169,11 @@
       </c>
       <c r="E59">
         <f t="shared" si="3"/>
-        <v>1.36</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="F59">
         <f t="shared" si="4"/>
-        <v>1.36</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="G59">
         <v>1</v>
@@ -2183,10 +2187,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C60">
-        <v>72.477999999999994</v>
+        <v>7.7850000000000001</v>
       </c>
       <c r="D60">
         <f t="shared" si="2"/>
@@ -2194,11 +2198,11 @@
       </c>
       <c r="E60">
         <f t="shared" si="3"/>
-        <v>72.477999999999994</v>
+        <v>7.7850000000000001</v>
       </c>
       <c r="F60">
         <f t="shared" si="4"/>
-        <v>72.477999999999994</v>
+        <v>7.7850000000000001</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -2212,10 +2216,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C61">
-        <v>0.13100000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="D61">
         <f t="shared" si="2"/>
@@ -2223,11 +2227,11 @@
       </c>
       <c r="E61">
         <f t="shared" si="3"/>
-        <v>0.13100000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="F61">
         <f t="shared" si="4"/>
-        <v>0.13100000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -2241,10 +2245,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C62">
-        <v>22.033999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="D62">
         <f t="shared" si="2"/>
@@ -2252,11 +2256,11 @@
       </c>
       <c r="E62">
         <f t="shared" si="3"/>
-        <v>22.033999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="F62">
         <f t="shared" si="4"/>
-        <v>22.033999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -2270,10 +2274,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C63">
-        <v>3.2839999999999998</v>
+        <v>72.477999999999994</v>
       </c>
       <c r="D63">
         <f t="shared" si="2"/>
@@ -2281,11 +2285,11 @@
       </c>
       <c r="E63">
         <f t="shared" si="3"/>
-        <v>3.2839999999999998</v>
+        <v>72.477999999999994</v>
       </c>
       <c r="F63">
         <f t="shared" si="4"/>
-        <v>3.2839999999999998</v>
+        <v>72.477999999999994</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -2299,10 +2303,10 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C64">
-        <v>35.752000000000002</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="D64">
         <f t="shared" si="2"/>
@@ -2310,16 +2314,103 @@
       </c>
       <c r="E64">
         <f t="shared" si="3"/>
-        <v>35.752000000000002</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="F64">
         <f t="shared" si="4"/>
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>74</v>
+      </c>
+      <c r="C65">
+        <v>22.033999999999999</v>
+      </c>
+      <c r="D65">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <f t="shared" si="3"/>
+        <v>22.033999999999999</v>
+      </c>
+      <c r="F65">
+        <f t="shared" si="4"/>
+        <v>22.033999999999999</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>75</v>
+      </c>
+      <c r="C66">
+        <v>3.2839999999999998</v>
+      </c>
+      <c r="D66">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <f t="shared" si="3"/>
+        <v>3.2839999999999998</v>
+      </c>
+      <c r="F66">
+        <f t="shared" si="4"/>
+        <v>3.2839999999999998</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>76</v>
+      </c>
+      <c r="C67">
         <v>35.752000000000002</v>
       </c>
-      <c r="G64">
-        <v>1</v>
-      </c>
-      <c r="H64" t="s">
+      <c r="D67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E67">
+        <f t="shared" si="3"/>
+        <v>35.752000000000002</v>
+      </c>
+      <c r="F67">
+        <f t="shared" si="4"/>
+        <v>35.752000000000002</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67" t="s">
         <v>10</v>
       </c>
     </row>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmunip.CAMPUS\source\repos\ABM-NM-optimization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C141CB2-284A-4BA7-9291-C48AA37AE700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1866BF85-0F64-4A90-AEE6-FC5B8EEDFB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6075" yWindow="2325" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14303" yWindow="-98" windowWidth="28995" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -325,12 +325,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1317,7 +1316,7 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26">
         <v>10</v>
       </c>
       <c r="F26">
@@ -1440,10 +1439,10 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="E31" s="4">
-        <v>10</v>
-      </c>
-      <c r="F31" s="4">
+      <c r="E31">
+        <v>10</v>
+      </c>
+      <c r="F31">
         <v>70</v>
       </c>
       <c r="G31">

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmunip.CAMPUS\source\repos\ABM-NM-optimization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1866BF85-0F64-4A90-AEE6-FC5B8EEDFB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBBB0915-F895-47A8-B3CA-B325DDD7F822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14303" yWindow="-98" windowWidth="28995" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5670" yWindow="3720" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="81">
   <si>
     <t>Mean</t>
   </si>
@@ -731,6 +731,9 @@
       <c r="G3">
         <v>1</v>
       </c>
+      <c r="H3" t="s">
+        <v>10</v>
+      </c>
       <c r="J3">
         <v>1</v>
       </c>
@@ -761,6 +764,9 @@
       <c r="G4">
         <v>1</v>
       </c>
+      <c r="H4" t="s">
+        <v>10</v>
+      </c>
       <c r="J4">
         <v>2</v>
       </c>
@@ -791,6 +797,9 @@
       <c r="G5">
         <v>3</v>
       </c>
+      <c r="H5" t="s">
+        <v>10</v>
+      </c>
       <c r="J5">
         <v>3</v>
       </c>
@@ -821,6 +830,9 @@
       <c r="G6">
         <v>1</v>
       </c>
+      <c r="H6" t="s">
+        <v>10</v>
+      </c>
       <c r="J6">
         <v>4</v>
       </c>
@@ -851,6 +863,9 @@
       <c r="G7">
         <v>1</v>
       </c>
+      <c r="H7" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
@@ -875,6 +890,9 @@
       <c r="G8">
         <v>1</v>
       </c>
+      <c r="H8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
@@ -899,6 +917,9 @@
       <c r="G9">
         <v>1</v>
       </c>
+      <c r="H9" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
@@ -923,6 +944,9 @@
       <c r="G10">
         <v>1</v>
       </c>
+      <c r="H10" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
@@ -946,6 +970,9 @@
       </c>
       <c r="G11">
         <v>1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -971,6 +998,9 @@
       <c r="G12">
         <v>1</v>
       </c>
+      <c r="H12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
@@ -995,6 +1025,9 @@
       <c r="G13">
         <v>1</v>
       </c>
+      <c r="H13" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
@@ -1019,6 +1052,9 @@
       <c r="G14">
         <v>1</v>
       </c>
+      <c r="H14" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
@@ -1043,6 +1079,9 @@
       <c r="G15">
         <v>1</v>
       </c>
+      <c r="H15" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
@@ -1235,20 +1274,23 @@
         <v>36</v>
       </c>
       <c r="C23">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="D23">
         <f t="shared" si="0"/>
-        <v>24.75</v>
+        <v>55</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="F23">
-        <v>100</v>
+        <v>260</v>
       </c>
       <c r="G23">
         <v>1</v>
+      </c>
+      <c r="H23" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1301,6 +1343,9 @@
       <c r="G25">
         <v>1</v>
       </c>
+      <c r="H25" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26">
@@ -1349,6 +1394,9 @@
       <c r="G27">
         <v>1</v>
       </c>
+      <c r="H27" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28">
@@ -1373,6 +1421,9 @@
       <c r="G28">
         <v>1</v>
       </c>
+      <c r="H28" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29">
@@ -1397,6 +1448,9 @@
       <c r="G29">
         <v>1</v>
       </c>
+      <c r="H29" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30">
@@ -1499,6 +1553,9 @@
       <c r="G33">
         <v>1</v>
       </c>
+      <c r="H33" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34">
@@ -1655,6 +1712,9 @@
       <c r="G39">
         <v>1</v>
       </c>
+      <c r="H39" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40">
@@ -1679,6 +1739,9 @@
       <c r="G40">
         <v>1</v>
       </c>
+      <c r="H40" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41">
@@ -1715,20 +1778,23 @@
         <v>53</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D42">
         <f t="shared" si="0"/>
-        <v>2.25</v>
+        <v>122.5</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F42">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="G42">
         <v>1</v>
+      </c>
+      <c r="H42" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -1805,6 +1871,9 @@
       <c r="G45">
         <v>2</v>
       </c>
+      <c r="H45" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46">
@@ -1883,6 +1952,9 @@
       <c r="G48">
         <v>1</v>
       </c>
+      <c r="H48" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49">
@@ -1907,6 +1979,9 @@
       <c r="G49">
         <v>1</v>
       </c>
+      <c r="H49" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50">
@@ -1931,6 +2006,9 @@
       <c r="G50">
         <v>1</v>
       </c>
+      <c r="H50" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51">
@@ -1955,6 +2033,9 @@
       <c r="G51">
         <v>1</v>
       </c>
+      <c r="H51" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52">
@@ -1979,6 +2060,9 @@
       <c r="G52">
         <v>1</v>
       </c>
+      <c r="H52" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53">
@@ -2002,6 +2086,9 @@
       </c>
       <c r="G53">
         <v>1</v>
+      </c>
+      <c r="H53" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmunip.CAMPUS\source\repos\ABM-NM-optimization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBBB0915-F895-47A8-B3CA-B325DDD7F822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BA35BB-600C-4AFD-A262-BBEA0A226DE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5670" yWindow="3720" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1122,16 +1122,16 @@
       </c>
       <c r="D17">
         <f t="shared" si="0"/>
-        <v>0.24975</v>
+        <v>1.2497499999999999</v>
       </c>
       <c r="E17">
         <v>1E-3</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1623,16 +1623,16 @@
       </c>
       <c r="D36">
         <f t="shared" si="0"/>
-        <v>0.24975</v>
+        <v>1.2497499999999999</v>
       </c>
       <c r="E36">
         <v>1E-3</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmunip.CAMPUS\source\repos\ABM-NM-optimization\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mcgill-my.sharepoint.com/personal/meghana_munipalle_mail_mcgill_ca/Documents/research/ABM/calipro-py/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BA35BB-600C-4AFD-A262-BBEA0A226DE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{99BA35BB-600C-4AFD-A262-BBEA0A226DE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A707F322-E745-475D-802A-E9C2BE5E351E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -645,14 +645,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K67"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" customWidth="1"/>
+    <col min="3" max="3" width="22.109375" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -678,7 +678,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -708,7 +708,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -741,7 +741,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -774,7 +774,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -807,7 +807,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -840,7 +840,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -867,7 +867,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -894,7 +894,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -921,7 +921,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -948,7 +948,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -975,7 +975,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1002,7 +1002,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1029,7 +1029,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1056,7 +1056,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1161,7 +1161,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1188,7 +1188,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1212,7 +1212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1320,7 +1320,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1355,7 +1355,7 @@
         <v>78</v>
       </c>
       <c r="C26">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D26">
         <f t="shared" si="0"/>
@@ -1371,7 +1371,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1398,7 +1398,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1425,7 +1425,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1452,7 +1452,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1487,7 +1487,7 @@
         <v>79</v>
       </c>
       <c r="C31">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D31">
         <f t="shared" si="0"/>
@@ -1503,7 +1503,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1530,7 +1530,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1743,7 +1743,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1770,7 +1770,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1805,7 +1805,7 @@
         <v>80</v>
       </c>
       <c r="C43">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D43">
         <f t="shared" si="0"/>
@@ -1821,7 +1821,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1875,7 +1875,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1929,7 +1929,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1983,7 +1983,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2037,7 +2037,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2064,7 +2064,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2091,7 +2091,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2123,7 +2123,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2152,7 +2152,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2181,7 +2181,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2210,7 +2210,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2239,7 +2239,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2326,7 +2326,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2384,7 +2384,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2471,7 +2471,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
